--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -211,37 +211,37 @@
     <t>Medium</t>
   </si>
   <si>
+    <t>docs/sprints/S0.3.md</t>
+  </si>
+  <si>
+    <t>Naming standards published</t>
+  </si>
+  <si>
+    <t>S0.4</t>
+  </si>
+  <si>
+    <t>Define Data Models</t>
+  </si>
+  <si>
+    <t>Data Model Draft</t>
+  </si>
+  <si>
+    <t>docs/sprints/S0.4.md</t>
+  </si>
+  <si>
+    <t>Core data models documented</t>
+  </si>
+  <si>
+    <t>S0.5</t>
+  </si>
+  <si>
+    <t>Define Bronze Silver Gold Strategy</t>
+  </si>
+  <si>
+    <t>Data Layer Design</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>docs/sprints/S0.3.md</t>
-  </si>
-  <si>
-    <t>Naming standards published</t>
-  </si>
-  <si>
-    <t>S0.4</t>
-  </si>
-  <si>
-    <t>Define Data Models</t>
-  </si>
-  <si>
-    <t>Data Model Draft</t>
-  </si>
-  <si>
-    <t>docs/sprints/S0.4.md</t>
-  </si>
-  <si>
-    <t>Core data models documented</t>
-  </si>
-  <si>
-    <t>S0.5</t>
-  </si>
-  <si>
-    <t>Define Bronze Silver Gold Strategy</t>
-  </si>
-  <si>
-    <t>Data Layer Design</t>
   </si>
   <si>
     <t>docs/sprints/S0.5.md</t>
@@ -1533,16 +1533,16 @@
         <v>63</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>55</v>
@@ -1554,28 +1554,28 @@
         <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>48</v>
@@ -1587,19 +1587,19 @@
         <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1632,7 +1632,7 @@
         <v>51</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -1644,7 +1644,7 @@
         <v>82</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -1665,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -1698,7 +1698,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5">
         <v>2</v>
@@ -1764,7 +1764,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1797,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1896,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2028,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
@@ -2094,7 +2094,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
@@ -2127,7 +2127,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
@@ -2160,7 +2160,7 @@
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
@@ -2259,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
@@ -2325,7 +2325,7 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
@@ -2391,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
@@ -2523,7 +2523,7 @@
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>174</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
@@ -2721,7 +2721,7 @@
         <v>174</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
@@ -2820,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2886,7 +2886,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
@@ -2952,7 +2952,7 @@
         <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
@@ -3117,7 +3117,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>

--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -241,25 +241,25 @@
     <t>Data Layer Design</t>
   </si>
   <si>
+    <t>docs/sprints/S0.5.md</t>
+  </si>
+  <si>
+    <t>Medallion architecture documented</t>
+  </si>
+  <si>
+    <t>S0.2,S0.4</t>
+  </si>
+  <si>
+    <t>S0.6</t>
+  </si>
+  <si>
+    <t>Define Physical Data Layout</t>
+  </si>
+  <si>
+    <t>Catalog / Schema / Dataset Structure</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>docs/sprints/S0.5.md</t>
-  </si>
-  <si>
-    <t>Medallion architecture documented</t>
-  </si>
-  <si>
-    <t>S0.2,S0.4</t>
-  </si>
-  <si>
-    <t>S0.6</t>
-  </si>
-  <si>
-    <t>Define Physical Data Layout</t>
-  </si>
-  <si>
-    <t>Catalog / Schema / Dataset Structure</t>
   </si>
   <si>
     <t>docs/sprints/S0.6.md</t>
@@ -1599,19 +1599,19 @@
         <v>51</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -1620,19 +1620,19 @@
         <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -1665,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -1698,7 +1698,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G10" s="5">
         <v>2</v>
@@ -1764,7 +1764,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1797,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1896,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2028,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
@@ -2094,7 +2094,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
@@ -2127,7 +2127,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
@@ -2160,7 +2160,7 @@
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
@@ -2259,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
@@ -2325,7 +2325,7 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
@@ -2391,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
@@ -2523,7 +2523,7 @@
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>174</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
@@ -2721,7 +2721,7 @@
         <v>174</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
@@ -2820,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2886,7 +2886,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
@@ -2952,7 +2952,7 @@
         <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
@@ -3117,7 +3117,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>

--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -178,7 +178,7 @@
     <t>Done</t>
   </si>
   <si>
-    <t>docs/sprints/S0.1.md</t>
+    <t>docs/project_scope.md</t>
   </si>
   <si>
     <t>Project scope documented</t>
@@ -193,7 +193,7 @@
     <t>Repository Structure</t>
   </si>
   <si>
-    <t>docs/sprints/S0.2.md</t>
+    <t>docs/architecture/architecture_decisions.md</t>
   </si>
   <si>
     <t>Folder structure approved</t>
@@ -211,7 +211,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>docs/sprints/S0.3.md</t>
+    <t>docs/naming_conventions.md</t>
   </si>
   <si>
     <t>Naming standards published</t>
@@ -226,7 +226,7 @@
     <t>Data Model Draft</t>
   </si>
   <si>
-    <t>docs/sprints/S0.4.md</t>
+    <t>docs/data_models.md</t>
   </si>
   <si>
     <t>Core data models documented</t>
@@ -241,7 +241,7 @@
     <t>Data Layer Design</t>
   </si>
   <si>
-    <t>docs/sprints/S0.5.md</t>
+    <t>docs/lakehouse_architecture.md</t>
   </si>
   <si>
     <t>Medallion architecture documented</t>
@@ -259,25 +259,25 @@
     <t>Catalog / Schema / Dataset Structure</t>
   </si>
   <si>
+    <t>docs/physical_data_layout.md</t>
+  </si>
+  <si>
+    <t>Physical layout approved</t>
+  </si>
+  <si>
+    <t>Strava Ingestion</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Create Strava Application</t>
+  </si>
+  <si>
+    <t>Client ID and Client Secret</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>docs/sprints/S0.6.md</t>
-  </si>
-  <si>
-    <t>Physical layout approved</t>
-  </si>
-  <si>
-    <t>Strava Ingestion</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>Create Strava Application</t>
-  </si>
-  <si>
-    <t>Client ID and Client Secret</t>
   </si>
   <si>
     <t>docs/sprints/S1.md</t>
@@ -1411,7 +1411,7 @@
     <col min="5" max="5" style="2" width="11.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="2" width="14.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="6" width="23.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="23.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="28.862142857142857" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="2" width="51.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="2" width="15.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="2" width="8.005" customWidth="1" bestFit="1"/>
@@ -1632,16 +1632,16 @@
         <v>51</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>71</v>
@@ -1650,22 +1650,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>89</v>
@@ -1698,7 +1698,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -1710,13 +1710,13 @@
         <v>93</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K9" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>94</v>
@@ -1731,7 +1731,7 @@
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G10" s="5">
         <v>2</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
@@ -1764,7 +1764,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>105</v>
@@ -1797,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>110</v>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>115</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>120</v>
@@ -1896,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2028,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
@@ -2094,7 +2094,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
@@ -2127,7 +2127,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
@@ -2160,7 +2160,7 @@
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
@@ -2259,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
@@ -2325,7 +2325,7 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
@@ -2391,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
@@ -2523,7 +2523,7 @@
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>174</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
@@ -2721,7 +2721,7 @@
         <v>174</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
@@ -2820,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2886,7 +2886,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
@@ -2952,7 +2952,7 @@
         <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
@@ -3117,7 +3117,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>

--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -277,22 +277,22 @@
     <t>Client ID and Client Secret</t>
   </si>
   <si>
+    <t>docs/sprints/S1.md</t>
+  </si>
+  <si>
+    <t>Create Strava Application completed</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>Implement OAuth Authentication</t>
+  </si>
+  <si>
+    <t>Refresh Token</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>docs/sprints/S1.md</t>
-  </si>
-  <si>
-    <t>Create Strava Application completed</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>Implement OAuth Authentication</t>
-  </si>
-  <si>
-    <t>Refresh Token</t>
   </si>
   <si>
     <t>docs/sprints/S2.md</t>
@@ -1665,16 +1665,16 @@
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="5">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>48</v>
@@ -1686,19 +1686,19 @@
         <v>82</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G10" s="5">
         <v>2</v>
@@ -1743,7 +1743,7 @@
         <v>98</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K10" s="1"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1797,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1896,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2028,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
@@ -2094,7 +2094,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
@@ -2127,7 +2127,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
@@ -2160,7 +2160,7 @@
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
@@ -2259,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
@@ -2325,7 +2325,7 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
@@ -2391,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
@@ -2523,7 +2523,7 @@
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>174</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
@@ -2721,7 +2721,7 @@
         <v>174</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
@@ -2820,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2886,7 +2886,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
@@ -2952,7 +2952,7 @@
         <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
@@ -3117,7 +3117,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>

--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -292,22 +292,22 @@
     <t>Refresh Token</t>
   </si>
   <si>
+    <t>docs/sprints/S2.md</t>
+  </si>
+  <si>
+    <t>Implement OAuth Authentication completed</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Extract Athlete Activities</t>
+  </si>
+  <si>
+    <t>activities.json</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>docs/sprints/S2.md</t>
-  </si>
-  <si>
-    <t>Implement OAuth Authentication completed</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>Extract Athlete Activities</t>
-  </si>
-  <si>
-    <t>activities.json</t>
   </si>
   <si>
     <t>docs/sprints/S3.md</t>
@@ -1007,7 +1007,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1452,7 +1452,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>47</v>
       </c>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="K7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>82</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -1698,40 +1698,40 @@
         <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="5">
-        <v>2</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>83</v>
       </c>
       <c r="K9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G10" s="5">
         <v>2</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="K10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="K11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1896,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2028,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
@@ -2094,7 +2094,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
@@ -2127,7 +2127,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
@@ -2160,7 +2160,7 @@
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
@@ -2193,7 +2193,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
@@ -2259,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
@@ -2325,7 +2325,7 @@
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
@@ -2391,7 +2391,7 @@
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
@@ -2424,7 +2424,7 @@
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
@@ -2523,7 +2523,7 @@
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>174</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
@@ -2721,7 +2721,7 @@
         <v>174</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
@@ -2754,7 +2754,7 @@
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
@@ -2820,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2886,7 +2886,7 @@
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
@@ -2952,7 +2952,7 @@
         <v>174</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>174</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
@@ -3117,7 +3117,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>

--- a/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
+++ b/docs/roadmap/Fitness_Data_Platform_Roadmap_v5.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="323">
   <si>
     <t>Decision ID</t>
   </si>
@@ -307,145 +307,148 @@
     <t>activities.json</t>
   </si>
   <si>
+    <t>docs/sprints/S3.md</t>
+  </si>
+  <si>
+    <t>Extract Athlete Activities completed</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>Incremental Bronze Ingestion</t>
+  </si>
+  <si>
+    <t>Organized Raw JSON Files</t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
-    <t>docs/sprints/S3.md</t>
-  </si>
-  <si>
-    <t>Extract Athlete Activities completed</t>
-  </si>
-  <si>
-    <t>S4</t>
+    <t>docs/sprints/S4.md</t>
+  </si>
+  <si>
+    <t>Store Raw Data in Bronze Layer completed</t>
+  </si>
+  <si>
+    <t>S3,S0.6</t>
+  </si>
+  <si>
+    <t>S5</t>
+  </si>
+  <si>
+    <t>Implement Incremental Loading</t>
+  </si>
+  <si>
+    <t>state.json</t>
+  </si>
+  <si>
+    <t>docs/sprints/S5.md</t>
+  </si>
+  <si>
+    <t>Implement Incremental Loading completed</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>Add Logging and Error Handling</t>
+  </si>
+  <si>
+    <t>Execution Logs</t>
+  </si>
+  <si>
+    <t>docs/sprints/S6.md</t>
+  </si>
+  <si>
+    <t>Add Logging and Error Handling completed</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>Add Unit Tests</t>
+  </si>
+  <si>
+    <t>Test Suite</t>
+  </si>
+  <si>
+    <t>docs/sprints/S7.md</t>
+  </si>
+  <si>
+    <t>Add Unit Tests completed</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>Improve Project Documentation</t>
+  </si>
+  <si>
+    <t>Complete README</t>
+  </si>
+  <si>
+    <t>docs/sprints/S8.md</t>
+  </si>
+  <si>
+    <t>Improve Project Documentation completed</t>
+  </si>
+  <si>
+    <t>S1-S7</t>
+  </si>
+  <si>
+    <t>Google Tasks Ingestion</t>
+  </si>
+  <si>
+    <t>S9</t>
+  </si>
+  <si>
+    <t>Create Google Cloud Project</t>
+  </si>
+  <si>
+    <t>API Credentials</t>
+  </si>
+  <si>
+    <t>docs/sprints/S9.md</t>
+  </si>
+  <si>
+    <t>Create Google Cloud Project completed</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Implement Google Tasks Authentication</t>
+  </si>
+  <si>
+    <t>OAuth Integration</t>
+  </si>
+  <si>
+    <t>docs/sprints/S10.md</t>
+  </si>
+  <si>
+    <t>Implement Google Tasks Authentication completed</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Extract Tasks Data</t>
+  </si>
+  <si>
+    <t>tasks.json</t>
+  </si>
+  <si>
+    <t>docs/sprints/S11.md</t>
+  </si>
+  <si>
+    <t>Extract Tasks Data completed</t>
+  </si>
+  <si>
+    <t>S12</t>
   </si>
   <si>
     <t>Store Raw Data in Bronze Layer</t>
-  </si>
-  <si>
-    <t>Organized Raw JSON Files</t>
-  </si>
-  <si>
-    <t>docs/sprints/S4.md</t>
-  </si>
-  <si>
-    <t>Store Raw Data in Bronze Layer completed</t>
-  </si>
-  <si>
-    <t>S3,S0.6</t>
-  </si>
-  <si>
-    <t>S5</t>
-  </si>
-  <si>
-    <t>Implement Incremental Loading</t>
-  </si>
-  <si>
-    <t>state.json</t>
-  </si>
-  <si>
-    <t>docs/sprints/S5.md</t>
-  </si>
-  <si>
-    <t>Implement Incremental Loading completed</t>
-  </si>
-  <si>
-    <t>S6</t>
-  </si>
-  <si>
-    <t>Add Logging and Error Handling</t>
-  </si>
-  <si>
-    <t>Execution Logs</t>
-  </si>
-  <si>
-    <t>docs/sprints/S6.md</t>
-  </si>
-  <si>
-    <t>Add Logging and Error Handling completed</t>
-  </si>
-  <si>
-    <t>S7</t>
-  </si>
-  <si>
-    <t>Add Unit Tests</t>
-  </si>
-  <si>
-    <t>Test Suite</t>
-  </si>
-  <si>
-    <t>docs/sprints/S7.md</t>
-  </si>
-  <si>
-    <t>Add Unit Tests completed</t>
-  </si>
-  <si>
-    <t>S8</t>
-  </si>
-  <si>
-    <t>Improve Project Documentation</t>
-  </si>
-  <si>
-    <t>Complete README</t>
-  </si>
-  <si>
-    <t>docs/sprints/S8.md</t>
-  </si>
-  <si>
-    <t>Improve Project Documentation completed</t>
-  </si>
-  <si>
-    <t>S1-S7</t>
-  </si>
-  <si>
-    <t>Google Tasks Ingestion</t>
-  </si>
-  <si>
-    <t>S9</t>
-  </si>
-  <si>
-    <t>Create Google Cloud Project</t>
-  </si>
-  <si>
-    <t>API Credentials</t>
-  </si>
-  <si>
-    <t>docs/sprints/S9.md</t>
-  </si>
-  <si>
-    <t>Create Google Cloud Project completed</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Implement Google Tasks Authentication</t>
-  </si>
-  <si>
-    <t>OAuth Integration</t>
-  </si>
-  <si>
-    <t>docs/sprints/S10.md</t>
-  </si>
-  <si>
-    <t>Implement Google Tasks Authentication completed</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Extract Tasks Data</t>
-  </si>
-  <si>
-    <t>tasks.json</t>
-  </si>
-  <si>
-    <t>docs/sprints/S11.md</t>
-  </si>
-  <si>
-    <t>Extract Tasks Data completed</t>
-  </si>
-  <si>
-    <t>S12</t>
   </si>
   <si>
     <t>docs/sprints/S12.md</t>
@@ -1731,16 +1734,16 @@
         <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="5">
-        <v>2</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>88</v>
@@ -1752,19 +1755,19 @@
         <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" s="5">
         <v>2</v>
@@ -1797,7 +1800,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
@@ -1809,7 +1812,7 @@
         <v>109</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K12" s="1"/>
     </row>
@@ -1830,7 +1833,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G13" s="5">
         <v>2</v>
@@ -1863,7 +1866,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
@@ -1896,7 +1899,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G15" s="5">
         <v>2</v>
@@ -1929,7 +1932,7 @@
         <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G16" s="5">
         <v>2</v>
@@ -1962,7 +1965,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -1995,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G18" s="5">
         <v>2</v>
@@ -2019,28 +2022,28 @@
         <v>142</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G19" s="5">
         <v>2</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>103</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K19" s="1"/>
     </row>
@@ -2049,7 +2052,7 @@
         <v>126</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>106</v>
@@ -2061,13 +2064,13 @@
         <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G20" s="5">
         <v>2</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>109</v>
@@ -2082,1054 +2085,1054 @@
         <v>126</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G21" s="5">
         <v>2</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K21" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G22" s="5">
         <v>2</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K22" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G23" s="5">
         <v>2</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K23" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K24" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G25" s="5">
         <v>2</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K25" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G26" s="5">
         <v>2</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K26" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G27" s="5">
         <v>2</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K27" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G28" s="5">
         <v>2</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K28" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G29" s="5">
         <v>2</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K29" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G30" s="5">
         <v>2</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K30" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G31" s="5">
         <v>2</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K31" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G32" s="5">
         <v>2</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K32" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G33" s="5">
         <v>2</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K33" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G34" s="5">
         <v>2</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K34" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K35" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G36" s="5">
         <v>2</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K36" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G37" s="5">
         <v>2</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K37" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K38" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G39" s="5">
         <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K39" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G40" s="5">
         <v>2</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K40" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G41" s="5">
         <v>2</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K41" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G42" s="5">
         <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K42" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G43" s="5">
         <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K43" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K44" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K45" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G46" s="5">
         <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K46" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K47" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K48" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K49" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G50" s="5">
         <v>2</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K50" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G51" s="5">
         <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K51" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G52" s="5">
         <v>2</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K52" s="1"/>
     </row>
